--- a/forms/trg/Formulir_TRG_cbmc.xlsx
+++ b/forms/trg/Formulir_TRG_cbmc.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B29)</f>
+        <f>COUNTA(Anggota!B5:B30)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F29)</f>
+        <f>COUNTA(Anggota!F5:F30)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,22 +925,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Satria Astazaury Awal</t>
+          <t>Prof. Muhammad Aswad, S.Si., M.Si., Ph.D., Apt.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Faculty of Pharmacy Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Pharmacognosy and Phytochemistry</t>
+          <t>Medicinal Chemistry, Chemical Biology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -949,7 +945,11 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57196445637</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -962,22 +962,22 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Raihan</t>
+          <t>Satria Astazaury Awal</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Pharmacy, Hasanuddin University</t>
+          <t>Faculty of Pharmacy Hasanuddin University</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Phytochemistry, Natural Product Chemistry</t>
+          <t>Pharmacognosy and Phytochemistry</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -999,22 +999,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Herlina Rasyid, M.Si</t>
+          <t>Muhammad Raihan</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Mathematics and Natural Sciences</t>
+          <t>Faculty of Pharmacy, Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Phytochemistry, Natural Product Chemistry</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1036,22 +1036,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Andi Affandi, S.Si., M.Sc., Apt.</t>
+          <t>Dr. Herlina Rasyid, M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Pharmacy, Hasanuddin University</t>
+          <t>Faculty of Mathematics and Natural Sciences</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Pharmaceutical Chemistry</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1073,22 +1073,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>dr. Andi Rofian Sultan, M.Sc., Ph.D., Sp.MK</t>
+          <t>Andi Affandi, S.Si., M.Sc., Apt.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Medicine, Hasanuddin University</t>
+          <t>Faculty of Pharmacy, Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Microbiology</t>
+          <t>Pharmaceutical Chemistry</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1110,20 +1110,24 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Takenori Tomohiro, Ph.D</t>
+          <t>dr. Andi Rofian Sultan, M.Sc., Ph.D., Sp.MK</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>University of Toyama, Japan</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="n"/>
+          <t>Faculty of Medicine, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Microbiology</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1143,17 +1147,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Makoto Hashimoto, Ph.D</t>
+          <t>Prof. Takenori Tomohiro, Ph.D</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Hokkaido University, Japan</t>
+          <t>University of Toyama, Japan</t>
         </is>
       </c>
       <c r="E11" s="11" t="n"/>
@@ -1176,17 +1180,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Prof. Kenji Arakawa, Ph.D</t>
+          <t>Prof. Makoto Hashimoto, Ph.D</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Hiroshima University, Japan</t>
+          <t>Hokkaido University, Japan</t>
         </is>
       </c>
       <c r="E12" s="11" t="n"/>
@@ -1209,20 +1213,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Zetryana Puteri Tachrim, Ph.D</t>
+          <t>Prof. Kenji Arakawa, Ph.D</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>BRIN</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Hiroshima University, Japan</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1242,12 +1246,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr.Phil. Ratna Dini Haryuni</t>
+          <t>Zetryana Puteri Tachrim, Ph.D</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1275,20 +1279,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Muh. Arfandy Gunawan</t>
+          <t>Dr.Phil. Ratna Dini Haryuni</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>BRIN</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1308,15 +1312,19 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Ihfar Apriyati Ilham</t>
+          <t>Muh. Arfandy Gunawan</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n"/>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E16" s="11" t="n"/>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
@@ -1337,12 +1345,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Arifuddin Yunus</t>
+          <t>Ihfar Apriyati Ilham</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1364,10 +1372,22 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Arifuddin Yunus</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D18" s="12" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Chemical Biology examines the functions of biological systems through chemical methodologies, while Medicinal chemistry involves the design and enhancement of molecules to make novel pharmaceuticals or refine current ones. It entails employing chemical methodologies to formulate and synthesis novel compounds that are both safe and efficacious.</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -1375,7 +1395,11 @@
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1564,15 +1588,32 @@
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="12" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
